--- a/public/plantilla-presupuesto-unificado.xlsx
+++ b/public/plantilla-presupuesto-unificado.xlsx
@@ -17584,8 +17584,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A13:G513"/>
-  <mergeCells count="15">
-    <mergeCell ref="C514:F514"/>
+  <mergeCells count="13">
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="C522:F522"/>
@@ -17595,7 +17594,6 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="C514:G514"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A10:G10"/>

--- a/public/plantilla-presupuesto-unificado.xlsx
+++ b/public/plantilla-presupuesto-unificado.xlsx
@@ -10125,32 +10125,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>2766370</colOff>
-      <row>8</row>
-      <rowOff>172889</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2766370</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>172889</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3312000" cy="1584000"/>
@@ -10162,11 +10162,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-presupuesto-unificado.xlsx
+++ b/public/plantilla-presupuesto-unificado.xlsx
@@ -10370,8 +10370,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="392" t="n"/>
-      <c r="C1" s="392" t="n"/>
-      <c r="D1" s="738" t="inlineStr">
+      <c r="C1" s="738" t="inlineStr">
         <is>
           <t>PRESUPUESTO DE OBRA</t>
         </is>
@@ -10379,11 +10378,9 @@
     </row>
     <row r="2">
       <c r="A2" s="392" t="n"/>
-      <c r="C2" s="643" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="392" t="n"/>
-      <c r="C3" s="643" t="n"/>
     </row>
     <row r="4" ht="4.95" customHeight="1" s="565">
       <c r="A4" s="392" t="n"/>
@@ -10407,8 +10404,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" s="565">
       <c r="A6" s="392" t="n"/>
-      <c r="C6" s="643" t="n"/>
-      <c r="D6" s="573" t="inlineStr">
+      <c r="C6" s="573" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
@@ -10427,8 +10423,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="565">
       <c r="A7" s="392" t="n"/>
-      <c r="C7" s="643" t="n"/>
-      <c r="D7" s="568" t="inlineStr">
+      <c r="C7" s="568" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
@@ -10502,9 +10497,9 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B12" s="746" t="n"/>
+      <c r="B12" s="747" t="n"/>
       <c r="C12" s="746" t="n"/>
-      <c r="D12" s="747" t="n"/>
+      <c r="D12" s="746" t="n"/>
       <c r="E12" s="746" t="n"/>
       <c r="F12" s="116" t="inlineStr">
         <is>
@@ -17627,20 +17622,19 @@
     </row>
   </sheetData>
   <autoFilter ref="A13:G513"/>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D6:E6"/>
     <mergeCell ref="C522:F522"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D1:G3"/>
+    <mergeCell ref="C1:G3"/>
+    <mergeCell ref="B12:E12"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="C7:E7"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>

--- a/public/plantilla-presupuesto-unificado.xlsx
+++ b/public/plantilla-presupuesto-unificado.xlsx
@@ -10363,9 +10363,6 @@
     <col width="13" customWidth="1" style="565" min="5" max="5"/>
     <col width="19" customWidth="1" style="565" min="6" max="6"/>
     <col width="23" customWidth="1" style="565" min="7" max="7"/>
-    <col width="4" customWidth="1" style="565" min="8" max="8"/>
-    <col width="46" customWidth="1" style="565" min="9" max="9"/>
-    <col width="22" customWidth="1" style="565" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10548,11 +10545,6 @@
           <t>Valor Total</t>
         </is>
       </c>
-      <c r="I13" s="1406" t="inlineStr">
-        <is>
-          <t>RESUMEN POR CAPÍTULO (automático)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1409" t="n"/>
@@ -10565,16 +10557,6 @@
         <f>E14*F14</f>
         <v/>
       </c>
-      <c r="I14" s="1414" t="inlineStr">
-        <is>
-          <t>Capítulo</t>
-        </is>
-      </c>
-      <c r="J14" s="1414" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1409" t="n"/>
@@ -10587,15 +10569,6 @@
         <f>E15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="1410" t="inlineStr">
-        <is>
-          <t>PRELIMINARES</t>
-        </is>
-      </c>
-      <c r="J15" s="1413">
-        <f>SUMIF(B14:B512,I15,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1409" t="n"/>
@@ -10608,15 +10581,6 @@
         <f>E16*F16</f>
         <v/>
       </c>
-      <c r="I16" s="1410" t="inlineStr">
-        <is>
-          <t>MOVIMIENTO DE TIERRAS</t>
-        </is>
-      </c>
-      <c r="J16" s="1413">
-        <f>SUMIF(B14:B512,I16,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1409" t="n"/>
@@ -10629,15 +10593,6 @@
         <f>E17*F17</f>
         <v/>
       </c>
-      <c r="I17" s="1410" t="inlineStr">
-        <is>
-          <t>CIMENTACIONES</t>
-        </is>
-      </c>
-      <c r="J17" s="1413">
-        <f>SUMIF(B14:B512,I17,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1409" t="n"/>
@@ -10650,15 +10605,6 @@
         <f>E18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="1410" t="inlineStr">
-        <is>
-          <t>ESTRUCTURA</t>
-        </is>
-      </c>
-      <c r="J18" s="1413">
-        <f>SUMIF(B14:B512,I18,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1409" t="n"/>
@@ -10671,15 +10617,6 @@
         <f>E19*F19</f>
         <v/>
       </c>
-      <c r="I19" s="1410" t="inlineStr">
-        <is>
-          <t>MAMPOSTERÍA</t>
-        </is>
-      </c>
-      <c r="J19" s="1413">
-        <f>SUMIF(B14:B512,I19,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1409" t="n"/>
@@ -10692,15 +10629,6 @@
         <f>E20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="1410" t="inlineStr">
-        <is>
-          <t>CUBIERTAS</t>
-        </is>
-      </c>
-      <c r="J20" s="1413">
-        <f>SUMIF(B14:B512,I20,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1409" t="n"/>
@@ -10713,15 +10641,6 @@
         <f>E21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="1410" t="inlineStr">
-        <is>
-          <t>IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
-      <c r="J21" s="1413">
-        <f>SUMIF(B14:B512,I21,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1409" t="n"/>
@@ -10734,15 +10653,6 @@
         <f>E22*F22</f>
         <v/>
       </c>
-      <c r="I22" s="1410" t="inlineStr">
-        <is>
-          <t>PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
-      <c r="J22" s="1413">
-        <f>SUMIF(B14:B512,I22,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1409" t="n"/>
@@ -10755,15 +10665,6 @@
         <f>E23*F23</f>
         <v/>
       </c>
-      <c r="I23" s="1410" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="J23" s="1413">
-        <f>SUMIF(B14:B512,I23,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1409" t="n"/>
@@ -10776,15 +10677,6 @@
         <f>E24*F24</f>
         <v/>
       </c>
-      <c r="I24" s="1410" t="inlineStr">
-        <is>
-          <t>PINTURA</t>
-        </is>
-      </c>
-      <c r="J24" s="1413">
-        <f>SUMIF(B14:B512,I24,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1409" t="n"/>
@@ -10797,15 +10689,6 @@
         <f>E25*F25</f>
         <v/>
       </c>
-      <c r="I25" s="1410" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
-      <c r="J25" s="1413">
-        <f>SUMIF(B14:B512,I25,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1409" t="n"/>
@@ -10818,15 +10701,6 @@
         <f>E26*F26</f>
         <v/>
       </c>
-      <c r="I26" s="1410" t="inlineStr">
-        <is>
-          <t>VIDRIOS</t>
-        </is>
-      </c>
-      <c r="J26" s="1413">
-        <f>SUMIF(B14:B512,I26,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="1409" t="n"/>
@@ -10839,15 +10713,6 @@
         <f>E27*F27</f>
         <v/>
       </c>
-      <c r="I27" s="1410" t="inlineStr">
-        <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
-        </is>
-      </c>
-      <c r="J27" s="1413">
-        <f>SUMIF(B14:B512,I27,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1409" t="n"/>
@@ -10860,15 +10725,6 @@
         <f>E28*F28</f>
         <v/>
       </c>
-      <c r="I28" s="1410" t="inlineStr">
-        <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="J28" s="1413">
-        <f>SUMIF(B14:B512,I28,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1409" t="n"/>
@@ -10881,15 +10737,6 @@
         <f>E29*F29</f>
         <v/>
       </c>
-      <c r="I29" s="1410" t="inlineStr">
-        <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="J29" s="1413">
-        <f>SUMIF(B14:B512,I29,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="1409" t="n"/>
@@ -10902,15 +10749,6 @@
         <f>E30*F30</f>
         <v/>
       </c>
-      <c r="I30" s="1410" t="inlineStr">
-        <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
-        </is>
-      </c>
-      <c r="J30" s="1413">
-        <f>SUMIF(B14:B512,I30,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1409" t="n"/>
@@ -10923,15 +10761,6 @@
         <f>E31*F31</f>
         <v/>
       </c>
-      <c r="I31" s="1410" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="J31" s="1413">
-        <f>SUMIF(B14:B512,I31,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="1409" t="n"/>
@@ -10944,15 +10773,6 @@
         <f>E32*F32</f>
         <v/>
       </c>
-      <c r="I32" s="1410" t="inlineStr">
-        <is>
-          <t>URBANISMO Y EXTERIORES</t>
-        </is>
-      </c>
-      <c r="J32" s="1413">
-        <f>SUMIF(B14:B512,I32,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1409" t="n"/>
@@ -10965,15 +10785,6 @@
         <f>E33*F33</f>
         <v/>
       </c>
-      <c r="I33" s="1410" t="inlineStr">
-        <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="J33" s="1413">
-        <f>SUMIF(B14:B512,I33,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1409" t="n"/>
@@ -10986,15 +10797,6 @@
         <f>E34*F34</f>
         <v/>
       </c>
-      <c r="I34" s="1410" t="inlineStr">
-        <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="J34" s="1413">
-        <f>SUMIF(B14:B512,I34,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1409" t="n"/>
@@ -11007,15 +10809,6 @@
         <f>E35*F35</f>
         <v/>
       </c>
-      <c r="I35" s="1410" t="inlineStr">
-        <is>
-          <t>ASCENSORES</t>
-        </is>
-      </c>
-      <c r="J35" s="1413">
-        <f>SUMIF(B14:B512,I35,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1409" t="n"/>
@@ -11028,15 +10821,6 @@
         <f>E36*F36</f>
         <v/>
       </c>
-      <c r="I36" s="1410" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="J36" s="1413">
-        <f>SUMIF(B14:B512,I36,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1409" t="n"/>
@@ -11049,15 +10833,6 @@
         <f>E37*F37</f>
         <v/>
       </c>
-      <c r="I37" s="1410" t="inlineStr">
-        <is>
-          <t>EXCAVACIONES</t>
-        </is>
-      </c>
-      <c r="J37" s="1413">
-        <f>SUMIF(B14:B512,I37,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="1409" t="n"/>
@@ -11070,15 +10845,6 @@
         <f>E38*F38</f>
         <v/>
       </c>
-      <c r="I38" s="1410" t="inlineStr">
-        <is>
-          <t>TERRAPLENES Y RELLENOS</t>
-        </is>
-      </c>
-      <c r="J38" s="1413">
-        <f>SUMIF(B14:B512,I38,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="1409" t="n"/>
@@ -11091,15 +10857,6 @@
         <f>E39*F39</f>
         <v/>
       </c>
-      <c r="I39" s="1410" t="inlineStr">
-        <is>
-          <t>SUBBASES Y BASES GRANULARES</t>
-        </is>
-      </c>
-      <c r="J39" s="1413">
-        <f>SUMIF(B14:B512,I39,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1409" t="n"/>
@@ -11112,15 +10869,6 @@
         <f>E40*F40</f>
         <v/>
       </c>
-      <c r="I40" s="1410" t="inlineStr">
-        <is>
-          <t>PAVIMENTOS ASFÁLTICOS</t>
-        </is>
-      </c>
-      <c r="J40" s="1413">
-        <f>SUMIF(B14:B512,I40,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1409" t="n"/>
@@ -11133,15 +10881,6 @@
         <f>E41*F41</f>
         <v/>
       </c>
-      <c r="I41" s="1410" t="inlineStr">
-        <is>
-          <t>PAVIMENTO RÍGIDO</t>
-        </is>
-      </c>
-      <c r="J41" s="1413">
-        <f>SUMIF(B14:B512,I41,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1409" t="n"/>
@@ -11154,15 +10893,6 @@
         <f>E42*F42</f>
         <v/>
       </c>
-      <c r="I42" s="1410" t="inlineStr">
-        <is>
-          <t>ESTRUCTURAS Y PUENTES</t>
-        </is>
-      </c>
-      <c r="J42" s="1413">
-        <f>SUMIF(B14:B512,I42,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="1409" t="n"/>
@@ -11175,15 +10905,6 @@
         <f>E43*F43</f>
         <v/>
       </c>
-      <c r="I43" s="1410" t="inlineStr">
-        <is>
-          <t>OBRAS DE ESTABILIZACIÓN GEOTÉCNICA</t>
-        </is>
-      </c>
-      <c r="J43" s="1413">
-        <f>SUMIF(B14:B512,I43,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="1409" t="n"/>
@@ -11196,15 +10917,6 @@
         <f>E44*F44</f>
         <v/>
       </c>
-      <c r="I44" s="1410" t="inlineStr">
-        <is>
-          <t>OBRAS AMBIENTALES Y PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="J44" s="1413">
-        <f>SUMIF(B14:B512,I44,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="1409" t="n"/>
@@ -11217,15 +10929,6 @@
         <f>E45*F45</f>
         <v/>
       </c>
-      <c r="I45" s="1410" t="inlineStr">
-        <is>
-          <t>SEÑALIZACIÓN Y SEGURIDAD VIAL</t>
-        </is>
-      </c>
-      <c r="J45" s="1413">
-        <f>SUMIF(B14:B512,I45,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="1409" t="n"/>
@@ -11238,15 +10941,6 @@
         <f>E46*F46</f>
         <v/>
       </c>
-      <c r="I46" s="1410" t="inlineStr">
-        <is>
-          <t>TRANSPORTE Y GESTIÓN DE MATERIALES</t>
-        </is>
-      </c>
-      <c r="J46" s="1413">
-        <f>SUMIF(B14:B512,I46,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1409" t="n"/>
@@ -11259,15 +10953,6 @@
         <f>E47*F47</f>
         <v/>
       </c>
-      <c r="I47" s="1410" t="inlineStr">
-        <is>
-          <t>VARIOS Y OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="J47" s="1413">
-        <f>SUMIF(B14:B512,I47,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="1409" t="n"/>
@@ -11280,15 +10965,6 @@
         <f>E48*F48</f>
         <v/>
       </c>
-      <c r="I48" s="1410" t="inlineStr">
-        <is>
-          <t>CORTES Y EXCAVACIONES</t>
-        </is>
-      </c>
-      <c r="J48" s="1413">
-        <f>SUMIF(B14:B512,I48,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1409" t="n"/>
@@ -11301,15 +10977,6 @@
         <f>E49*F49</f>
         <v/>
       </c>
-      <c r="I49" s="1410" t="inlineStr">
-        <is>
-          <t>RELLENOS</t>
-        </is>
-      </c>
-      <c r="J49" s="1413">
-        <f>SUMIF(B14:B512,I49,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="1409" t="n"/>
@@ -11322,15 +10989,6 @@
         <f>E50*F50</f>
         <v/>
       </c>
-      <c r="I50" s="1410" t="inlineStr">
-        <is>
-          <t>PREPARACIÓN, SUMINISTRO E INSTALACIÓN  DE CONCRETO</t>
-        </is>
-      </c>
-      <c r="J50" s="1413">
-        <f>SUMIF(B14:B512,I50,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="1409" t="n"/>
@@ -11343,15 +11001,6 @@
         <f>E51*F51</f>
         <v/>
       </c>
-      <c r="I51" s="1410" t="inlineStr">
-        <is>
-          <t>JUNTAS</t>
-        </is>
-      </c>
-      <c r="J51" s="1413">
-        <f>SUMIF(B14:B512,I51,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="1409" t="n"/>
@@ -11364,15 +11013,6 @@
         <f>E52*F52</f>
         <v/>
       </c>
-      <c r="I52" s="1410" t="inlineStr">
-        <is>
-          <t>MORTEROS Y GROUTING</t>
-        </is>
-      </c>
-      <c r="J52" s="1413">
-        <f>SUMIF(B14:B512,I52,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="1409" t="n"/>
@@ -11385,15 +11025,6 @@
         <f>E53*F53</f>
         <v/>
       </c>
-      <c r="I53" s="1410" t="inlineStr">
-        <is>
-          <t>ACEROS DE REFUERZO</t>
-        </is>
-      </c>
-      <c r="J53" s="1413">
-        <f>SUMIF(B14:B512,I53,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="1409" t="n"/>
@@ -11406,15 +11037,6 @@
         <f>E54*F54</f>
         <v/>
       </c>
-      <c r="I54" s="1410" t="inlineStr">
-        <is>
-          <t>ESTRUCTURAS METÁLICAS</t>
-        </is>
-      </c>
-      <c r="J54" s="1413">
-        <f>SUMIF(B14:B512,I54,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="1409" t="n"/>
@@ -11427,15 +11049,6 @@
         <f>E55*F55</f>
         <v/>
       </c>
-      <c r="I55" s="1410" t="inlineStr">
-        <is>
-          <t>CERRAMIENTOS</t>
-        </is>
-      </c>
-      <c r="J55" s="1413">
-        <f>SUMIF(B14:B512,I55,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1409" t="n"/>
@@ -11448,15 +11061,6 @@
         <f>E56*F56</f>
         <v/>
       </c>
-      <c r="I56" s="1410" t="inlineStr">
-        <is>
-          <t>PAVIMENTACIÓN Y ESTABILIZACIÓN DE VÍAS</t>
-        </is>
-      </c>
-      <c r="J56" s="1413">
-        <f>SUMIF(B14:B512,I56,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1409" t="n"/>
@@ -11469,15 +11073,6 @@
         <f>E57*F57</f>
         <v/>
       </c>
-      <c r="I57" s="1410" t="inlineStr">
-        <is>
-          <t>SEÑALIZACIÓN DE VIAS</t>
-        </is>
-      </c>
-      <c r="J57" s="1413">
-        <f>SUMIF(B14:B512,I57,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1409" t="n"/>
@@ -11490,15 +11085,6 @@
         <f>E58*F58</f>
         <v/>
       </c>
-      <c r="I58" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN DE GEOTEXTILES</t>
-        </is>
-      </c>
-      <c r="J58" s="1413">
-        <f>SUMIF(B14:B512,I58,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1409" t="n"/>
@@ -11511,15 +11097,6 @@
         <f>E59*F59</f>
         <v/>
       </c>
-      <c r="I59" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN DE TUBERÍA</t>
-        </is>
-      </c>
-      <c r="J59" s="1413">
-        <f>SUMIF(B14:B512,I59,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1409" t="n"/>
@@ -11532,15 +11109,6 @@
         <f>E60*F60</f>
         <v/>
       </c>
-      <c r="I60" s="1410" t="inlineStr">
-        <is>
-          <t>DEMOLICIONES,  DESMANTELAMIENTOS Y RETIROS</t>
-        </is>
-      </c>
-      <c r="J60" s="1413">
-        <f>SUMIF(B14:B512,I60,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="1409" t="n"/>
@@ -11553,15 +11121,6 @@
         <f>E61*F61</f>
         <v/>
       </c>
-      <c r="I61" s="1410" t="inlineStr">
-        <is>
-          <t>DESMANTELAMIENTO DE ESTRUCTURAS METALICAS</t>
-        </is>
-      </c>
-      <c r="J61" s="1413">
-        <f>SUMIF(B14:B512,I61,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="1409" t="n"/>
@@ -11574,15 +11133,6 @@
         <f>E62*F62</f>
         <v/>
       </c>
-      <c r="I62" s="1410" t="inlineStr">
-        <is>
-          <t>SISTEMA CONTRA INCENDIO</t>
-        </is>
-      </c>
-      <c r="J62" s="1413">
-        <f>SUMIF(B14:B512,I62,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1409" t="n"/>
@@ -11595,15 +11145,6 @@
         <f>E63*F63</f>
         <v/>
       </c>
-      <c r="I63" s="1410" t="inlineStr">
-        <is>
-          <t>PREPARACIÓN  DE SUPERFICIE Y APLICACIÓN DE PINTURA PARA TUBERÍAS DESNUDAS</t>
-        </is>
-      </c>
-      <c r="J63" s="1413">
-        <f>SUMIF(B14:B512,I63,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="1409" t="n"/>
@@ -11616,15 +11157,6 @@
         <f>E64*F64</f>
         <v/>
       </c>
-      <c r="I64" s="1410" t="inlineStr">
-        <is>
-          <t>ENSAYOS NO DESTRUCTIVOS</t>
-        </is>
-      </c>
-      <c r="J64" s="1413">
-        <f>SUMIF(B14:B512,I64,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="1409" t="n"/>
@@ -11637,15 +11169,6 @@
         <f>E65*F65</f>
         <v/>
       </c>
-      <c r="I65" s="1410" t="inlineStr">
-        <is>
-          <t>PRUEBAS</t>
-        </is>
-      </c>
-      <c r="J65" s="1413">
-        <f>SUMIF(B14:B512,I65,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="1409" t="n"/>
@@ -11658,15 +11181,6 @@
         <f>E66*F66</f>
         <v/>
       </c>
-      <c r="I66" s="1410" t="inlineStr">
-        <is>
-          <t>EJECUCIÓN DE TIE-INS</t>
-        </is>
-      </c>
-      <c r="J66" s="1413">
-        <f>SUMIF(B14:B512,I66,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1409" t="n"/>
@@ -11679,15 +11193,6 @@
         <f>E67*F67</f>
         <v/>
       </c>
-      <c r="I67" s="1410" t="inlineStr">
-        <is>
-          <t>SOPORTES PARA TUBERÍAS</t>
-        </is>
-      </c>
-      <c r="J67" s="1413">
-        <f>SUMIF(B14:B512,I67,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1409" t="n"/>
@@ -11700,15 +11205,6 @@
         <f>E68*F68</f>
         <v/>
       </c>
-      <c r="I68" s="1410" t="inlineStr">
-        <is>
-          <t>DESMANTELAMIENTO</t>
-        </is>
-      </c>
-      <c r="J68" s="1413">
-        <f>SUMIF(B14:B512,I68,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1409" t="n"/>
@@ -11721,16 +11217,6 @@
         <f>E69*F69</f>
         <v/>
       </c>
-      <c r="I69" s="1410" t="inlineStr">
-        <is>
-          <t>INSTALACIÓN DE TUBERÍA EN TRAMOS ESPECIALES  
-(incluye transporte, cargue y descargue de tubería, tendido, doblado, alineación, soldadura, revestimiento de juntas, zanjado, bajado y tapado de tubería)</t>
-        </is>
-      </c>
-      <c r="J69" s="1413">
-        <f>SUMIF(B14:B512,I69,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1409" t="n"/>
@@ -11743,16 +11229,6 @@
         <f>E70*F70</f>
         <v/>
       </c>
-      <c r="I70" s="1410" t="inlineStr">
-        <is>
-          <t>PREFABRICACIÓN Y MONTAJE  DE TUBERÍA Y ACCESORIOS 
-(incluye transporte, corte, biselado, alineación y soldaduras)</t>
-        </is>
-      </c>
-      <c r="J70" s="1413">
-        <f>SUMIF(B14:B512,I70,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="1409" t="n"/>
@@ -11765,16 +11241,6 @@
         <f>E71*F71</f>
         <v/>
       </c>
-      <c r="I71" s="1410" t="inlineStr">
-        <is>
-          <t>MONTAJE DE VÁLVULAS, FILTROS, CHEQUES Y CIEGOS BRIDADOS  
-(incluye el suministro de empaques y espárragos con su respectivo torqueo)</t>
-        </is>
-      </c>
-      <c r="J71" s="1413">
-        <f>SUMIF(B14:B512,I71,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="1409" t="n"/>
@@ -11787,16 +11253,6 @@
         <f>E72*F72</f>
         <v/>
       </c>
-      <c r="I72" s="1410" t="inlineStr">
-        <is>
-          <t>INSTALACIÓN DE TUBERÍA  EN TRAMOS RECTOS  MAYORES DE 6 METROS DE LONGITUD SOBRE MARCOS H, PIPE RACK O ENTERRADA
-(incluye localización y replanteo de la tubería, tendido, corte, doblado, alineación, soldadura y revestimiento de junta)</t>
-        </is>
-      </c>
-      <c r="J72" s="1413">
-        <f>SUMIF(B14:B512,I72,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1409" t="n"/>
@@ -11809,15 +11265,6 @@
         <f>E73*F73</f>
         <v/>
       </c>
-      <c r="I73" s="1410" t="inlineStr">
-        <is>
-          <t>INSTRUMENTOS DE PRESIÓN</t>
-        </is>
-      </c>
-      <c r="J73" s="1413">
-        <f>SUMIF(B14:B512,I73,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1409" t="n"/>
@@ -11830,15 +11277,6 @@
         <f>E74*F74</f>
         <v/>
       </c>
-      <c r="I74" s="1410" t="inlineStr">
-        <is>
-          <t>INSTRUMENTOS DE TEMPERATURA</t>
-        </is>
-      </c>
-      <c r="J74" s="1413">
-        <f>SUMIF(B14:B512,I74,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="1409" t="n"/>
@@ -11851,15 +11289,6 @@
         <f>E75*F75</f>
         <v/>
       </c>
-      <c r="I75" s="1410" t="inlineStr">
-        <is>
-          <t>INSTRUMENTOS DE NIVEL</t>
-        </is>
-      </c>
-      <c r="J75" s="1413">
-        <f>SUMIF(B14:B512,I75,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="1409" t="n"/>
@@ -11872,15 +11301,6 @@
         <f>E76*F76</f>
         <v/>
       </c>
-      <c r="I76" s="1410" t="inlineStr">
-        <is>
-          <t>INSTRUMENTOS DE CORROSIÓN</t>
-        </is>
-      </c>
-      <c r="J76" s="1413">
-        <f>SUMIF(B14:B512,I76,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="1409" t="n"/>
@@ -11893,15 +11313,6 @@
         <f>E77*F77</f>
         <v/>
       </c>
-      <c r="I77" s="1410" t="inlineStr">
-        <is>
-          <t>VÁLVULAS DE ALIVIO DE PRESIÓN</t>
-        </is>
-      </c>
-      <c r="J77" s="1413">
-        <f>SUMIF(B14:B512,I77,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1409" t="n"/>
@@ -11914,15 +11325,6 @@
         <f>E78*F78</f>
         <v/>
       </c>
-      <c r="I78" s="1410" t="inlineStr">
-        <is>
-          <t>VÁLVULAS DE CONTROL</t>
-        </is>
-      </c>
-      <c r="J78" s="1413">
-        <f>SUMIF(B14:B512,I78,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1409" t="n"/>
@@ -11935,15 +11337,6 @@
         <f>E79*F79</f>
         <v/>
       </c>
-      <c r="I79" s="1410" t="inlineStr">
-        <is>
-          <t>CABLES DE INSTRUMENTACIÓN</t>
-        </is>
-      </c>
-      <c r="J79" s="1413">
-        <f>SUMIF(B14:B512,I79,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="1409" t="n"/>
@@ -11956,15 +11349,6 @@
         <f>E80*F80</f>
         <v/>
       </c>
-      <c r="I80" s="1410" t="inlineStr">
-        <is>
-          <t>CABLES DE COMUNICACIONES</t>
-        </is>
-      </c>
-      <c r="J80" s="1413">
-        <f>SUMIF(B14:B512,I80,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1409" t="n"/>
@@ -11977,15 +11361,6 @@
         <f>E81*F81</f>
         <v/>
       </c>
-      <c r="I81" s="1410" t="inlineStr">
-        <is>
-          <t>CONDULETAS</t>
-        </is>
-      </c>
-      <c r="J81" s="1413">
-        <f>SUMIF(B14:B512,I81,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1409" t="n"/>
@@ -11998,15 +11373,6 @@
         <f>E82*F82</f>
         <v/>
       </c>
-      <c r="I82" s="1410" t="inlineStr">
-        <is>
-          <t>SELLOS CORTAFUEGOS</t>
-        </is>
-      </c>
-      <c r="J82" s="1413">
-        <f>SUMIF(B14:B512,I82,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="1409" t="n"/>
@@ -12019,15 +11385,6 @@
         <f>E83*F83</f>
         <v/>
       </c>
-      <c r="I83" s="1410" t="inlineStr">
-        <is>
-          <t>CONDUIT FLEXIBLE</t>
-        </is>
-      </c>
-      <c r="J83" s="1413">
-        <f>SUMIF(B14:B512,I83,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="1409" t="n"/>
@@ -12040,15 +11397,6 @@
         <f>E84*F84</f>
         <v/>
       </c>
-      <c r="I84" s="1410" t="inlineStr">
-        <is>
-          <t>TUBING (NO APLICA PARA ITEMS DE PAGO QUE LO INCLUYEN EN EL MONTAJE)</t>
-        </is>
-      </c>
-      <c r="J84" s="1413">
-        <f>SUMIF(B14:B512,I84,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="1409" t="n"/>
@@ -12061,15 +11409,6 @@
         <f>E85*F85</f>
         <v/>
       </c>
-      <c r="I85" s="1410" t="inlineStr">
-        <is>
-          <t>UNIONES</t>
-        </is>
-      </c>
-      <c r="J85" s="1413">
-        <f>SUMIF(B14:B512,I85,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="1409" t="n"/>
@@ -12082,15 +11421,6 @@
         <f>E86*F86</f>
         <v/>
       </c>
-      <c r="I86" s="1410" t="inlineStr">
-        <is>
-          <t>REDUCCIONES</t>
-        </is>
-      </c>
-      <c r="J86" s="1413">
-        <f>SUMIF(B14:B512,I86,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="1409" t="n"/>
@@ -12103,15 +11433,6 @@
         <f>E87*F87</f>
         <v/>
       </c>
-      <c r="I87" s="1410" t="inlineStr">
-        <is>
-          <t>SOPORTE DE INSTRUMENTOS</t>
-        </is>
-      </c>
-      <c r="J87" s="1413">
-        <f>SUMIF(B14:B512,I87,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="1409" t="n"/>
@@ -12124,15 +11445,6 @@
         <f>E88*F88</f>
         <v/>
       </c>
-      <c r="I88" s="1410" t="inlineStr">
-        <is>
-          <t>POSTES</t>
-        </is>
-      </c>
-      <c r="J88" s="1413">
-        <f>SUMIF(B14:B512,I88,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="1409" t="n"/>
@@ -12145,15 +11457,6 @@
         <f>E89*F89</f>
         <v/>
       </c>
-      <c r="I89" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN DE CABLES DE BAJA TENSIÓN</t>
-        </is>
-      </c>
-      <c r="J89" s="1413">
-        <f>SUMIF(B14:B512,I89,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="1409" t="n"/>
@@ -12166,15 +11469,6 @@
         <f>E90*F90</f>
         <v/>
       </c>
-      <c r="I90" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN, PRUEBAS Y PUESTA EN SERVICIO DE CABLES DE MEDIA TENSIÓN</t>
-        </is>
-      </c>
-      <c r="J90" s="1413">
-        <f>SUMIF(B14:B512,I90,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="1409" t="n"/>
@@ -12187,15 +11481,6 @@
         <f>E91*F91</f>
         <v/>
       </c>
-      <c r="I91" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO, INSTALACIÓN, PRUEBAS Y PUESTA EN SERVICIO CABLE DE COBRE PARA PUESTA A TIERRA</t>
-        </is>
-      </c>
-      <c r="J91" s="1413">
-        <f>SUMIF(B14:B512,I91,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="1409" t="n"/>
@@ -12208,15 +11493,6 @@
         <f>E92*F92</f>
         <v/>
       </c>
-      <c r="I92" s="1410" t="inlineStr">
-        <is>
-          <t>ACCESORIOS DE PUESTA A TIERRA</t>
-        </is>
-      </c>
-      <c r="J92" s="1413">
-        <f>SUMIF(B14:B512,I92,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="1409" t="n"/>
@@ -12229,15 +11505,6 @@
         <f>E93*F93</f>
         <v/>
       </c>
-      <c r="I93" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN TUBERÍA CONDUIT RÍGIDA GALVANIZADA EN BANCO DE DUCTOS AÉREOS</t>
-        </is>
-      </c>
-      <c r="J93" s="1413">
-        <f>SUMIF(B14:B512,I93,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1409" t="n"/>
@@ -12250,15 +11517,6 @@
         <f>E94*F94</f>
         <v/>
       </c>
-      <c r="I94" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN ACCESORIOS PARA TUBERÍA CONDUIT</t>
-        </is>
-      </c>
-      <c r="J94" s="1413">
-        <f>SUMIF(B14:B512,I94,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="1409" t="n"/>
@@ -12271,15 +11529,6 @@
         <f>E95*F95</f>
         <v/>
       </c>
-      <c r="I95" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINSTRO E INSTALACIÓN DE ESTACIONES DE CONTROL</t>
-        </is>
-      </c>
-      <c r="J95" s="1413">
-        <f>SUMIF(B14:B512,I95,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="1409" t="n"/>
@@ -12292,15 +11541,6 @@
         <f>E96*F96</f>
         <v/>
       </c>
-      <c r="I96" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN TIPO EXTERIOR</t>
-        </is>
-      </c>
-      <c r="J96" s="1413">
-        <f>SUMIF(B14:B512,I96,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="1409" t="n"/>
@@ -12313,15 +11553,6 @@
         <f>E97*F97</f>
         <v/>
       </c>
-      <c r="I97" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO, INSTALACIÓN Y PUESTA EN SERVICIO DE CAJAS</t>
-        </is>
-      </c>
-      <c r="J97" s="1413">
-        <f>SUMIF(B14:B512,I97,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="1409" t="n"/>
@@ -12334,15 +11565,6 @@
         <f>E98*F98</f>
         <v/>
       </c>
-      <c r="I98" s="1410" t="inlineStr">
-        <is>
-          <t>TÍPICOS DE MONTAJE DE LLEGADA A INSTRUMENTOS Y CAJAS</t>
-        </is>
-      </c>
-      <c r="J98" s="1413">
-        <f>SUMIF(B14:B512,I98,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="1409" t="n"/>
@@ -12355,15 +11577,6 @@
         <f>E99*F99</f>
         <v/>
       </c>
-      <c r="I99" s="1410" t="inlineStr">
-        <is>
-          <t>SUMINISTRO E INSTALACIÓN DE CAJAS DE HALADO</t>
-        </is>
-      </c>
-      <c r="J99" s="1413">
-        <f>SUMIF(B14:B512,I99,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="1409" t="n"/>
@@ -12376,15 +11589,6 @@
         <f>E100*F100</f>
         <v/>
       </c>
-      <c r="I100" s="1410" t="inlineStr">
-        <is>
-          <t>RETIE</t>
-        </is>
-      </c>
-      <c r="J100" s="1413">
-        <f>SUMIF(B14:B512,I100,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="1409" t="n"/>
@@ -12397,15 +11601,6 @@
         <f>E101*F101</f>
         <v/>
       </c>
-      <c r="I101" s="1410" t="inlineStr">
-        <is>
-          <t>CERTIFICACIONES</t>
-        </is>
-      </c>
-      <c r="J101" s="1413">
-        <f>SUMIF(B14:B512,I101,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="1409" t="n"/>
@@ -12418,15 +11613,6 @@
         <f>E102*F102</f>
         <v/>
       </c>
-      <c r="I102" s="1410" t="inlineStr">
-        <is>
-          <t>DESMANTELAMIENTO DE LUMINARIAS</t>
-        </is>
-      </c>
-      <c r="J102" s="1413">
-        <f>SUMIF(B14:B512,I102,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="1409" t="n"/>
@@ -12439,15 +11625,6 @@
         <f>E103*F103</f>
         <v/>
       </c>
-      <c r="I103" s="1410" t="inlineStr">
-        <is>
-          <t>DESMANTELAMIENTO DE POSTES</t>
-        </is>
-      </c>
-      <c r="J103" s="1413">
-        <f>SUMIF(B14:B512,I103,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="1409" t="n"/>
@@ -12460,15 +11637,6 @@
         <f>E104*F104</f>
         <v/>
       </c>
-      <c r="I104" s="1410" t="inlineStr">
-        <is>
-          <t>DESMANTELAMIENTO DE LÍNEAS</t>
-        </is>
-      </c>
-      <c r="J104" s="1413">
-        <f>SUMIF(B14:B512,I104,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="1409" t="n"/>
@@ -12481,15 +11649,6 @@
         <f>E105*F105</f>
         <v/>
       </c>
-      <c r="I105" s="1410" t="inlineStr">
-        <is>
-          <t>TABLEROS</t>
-        </is>
-      </c>
-      <c r="J105" s="1413">
-        <f>SUMIF(B14:B512,I105,G14:G512)</f>
-        <v/>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="1409" t="n"/>
@@ -17622,14 +16781,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A13:G513"/>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="C522:F522"/>
     <mergeCell ref="C1:G3"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D5:E5"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A11:G11"/>
